--- a/ESC_Folder/TENCL040_ESC.xlsx
+++ b/ESC_Folder/TENCL040_ESC.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="106">
   <si>
     <t xml:space="preserve">Device Profile:</t>
   </si>
@@ -352,6 +352,111 @@
   </si>
   <si>
     <t xml:space="preserve">tx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x6010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARRAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Channel 1 (mA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1..8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REAL32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x6018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Channel 2 (mA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x6020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Channel 3 (mA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x6028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Channel 4 (mA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x6030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Channel 5 (mA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x6038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Channel 6 (mA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x6040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Channel 7 (mA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x6048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltage Channel 0 (mV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x6050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltage Channel 1 (mV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x6058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltage Channel 2 (mV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x6060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltage Channel 3 (mV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x6068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltage Channel 4 (mV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x6070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltage Channel 5 (mV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x6078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltage Channel 6 (mV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x6080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltage Channel 7 (mV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x6088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ML Inference (Channel)</t>
   </si>
   <si>
     <t xml:space="preserve">//0x7nnx</t>
@@ -3737,49 +3842,69 @@
       <c r="P159" s="21"/>
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B160" s="0"/>
-      <c r="C160" s="0"/>
-      <c r="D160" s="0"/>
-      <c r="E160" s="0"/>
-      <c r="F160" s="0"/>
-      <c r="G160" s="0"/>
-      <c r="H160" s="0"/>
-      <c r="I160" s="0"/>
-      <c r="J160" s="0"/>
-      <c r="K160" s="0"/>
-      <c r="L160" s="0"/>
-      <c r="M160" s="0"/>
-      <c r="N160" s="0"/>
-      <c r="O160" s="0"/>
-      <c r="P160" s="0"/>
+      <c r="B160" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C160" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="D160" s="21"/>
+      <c r="E160" s="24"/>
+      <c r="F160" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="G160" s="39"/>
+      <c r="H160" s="39"/>
+      <c r="I160" s="39"/>
+      <c r="L160" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M160" s="29"/>
+      <c r="N160" s="5"/>
+      <c r="O160" s="5"/>
+      <c r="P160" s="5"/>
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B161" s="0"/>
-      <c r="C161" s="0"/>
-      <c r="D161" s="0"/>
-      <c r="E161" s="0"/>
-      <c r="F161" s="0"/>
-      <c r="G161" s="0"/>
-      <c r="H161" s="0"/>
-      <c r="I161" s="0"/>
-      <c r="J161" s="0"/>
-      <c r="K161" s="0"/>
-      <c r="L161" s="0"/>
-      <c r="M161" s="0"/>
-      <c r="N161" s="0"/>
-      <c r="O161" s="0"/>
-      <c r="P161" s="0"/>
+      <c r="B161" s="21"/>
+      <c r="C161" s="29"/>
+      <c r="D161" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E161" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="F161" s="39"/>
+      <c r="G161" s="39"/>
+      <c r="H161" s="39"/>
+      <c r="I161" s="39"/>
+      <c r="L161" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M161" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="N161" s="5"/>
+      <c r="O161" s="5"/>
+      <c r="P161" s="5"/>
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B162" s="21"/>
-      <c r="C162" s="29"/>
+      <c r="B162" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C162" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="D162" s="21"/>
       <c r="E162" s="24"/>
-      <c r="F162" s="39"/>
+      <c r="F162" s="39" t="s">
+        <v>67</v>
+      </c>
       <c r="G162" s="39"/>
       <c r="H162" s="39"/>
       <c r="I162" s="39"/>
-      <c r="L162" s="29"/>
+      <c r="L162" s="29" t="s">
+        <v>56</v>
+      </c>
       <c r="M162" s="29"/>
       <c r="N162" s="5"/>
       <c r="O162" s="5"/>
@@ -3788,28 +3913,44 @@
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B163" s="21"/>
       <c r="C163" s="29"/>
-      <c r="D163" s="21"/>
-      <c r="E163" s="24"/>
+      <c r="D163" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E163" s="24" t="s">
+        <v>65</v>
+      </c>
       <c r="F163" s="39"/>
       <c r="G163" s="39"/>
       <c r="H163" s="39"/>
       <c r="I163" s="39"/>
-      <c r="L163" s="29"/>
-      <c r="M163" s="29"/>
+      <c r="L163" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M163" s="29" t="s">
+        <v>60</v>
+      </c>
       <c r="N163" s="5"/>
       <c r="O163" s="5"/>
       <c r="P163" s="5"/>
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B164" s="21"/>
-      <c r="C164" s="29"/>
+      <c r="B164" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C164" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="D164" s="21"/>
       <c r="E164" s="24"/>
-      <c r="F164" s="39"/>
+      <c r="F164" s="39" t="s">
+        <v>69</v>
+      </c>
       <c r="G164" s="39"/>
       <c r="H164" s="39"/>
       <c r="I164" s="39"/>
-      <c r="L164" s="29"/>
+      <c r="L164" s="29" t="s">
+        <v>56</v>
+      </c>
       <c r="M164" s="29"/>
       <c r="N164" s="5"/>
       <c r="O164" s="5"/>
@@ -3818,28 +3959,44 @@
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B165" s="21"/>
       <c r="C165" s="29"/>
-      <c r="D165" s="21"/>
-      <c r="E165" s="24"/>
+      <c r="D165" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E165" s="24" t="s">
+        <v>65</v>
+      </c>
       <c r="F165" s="39"/>
       <c r="G165" s="39"/>
       <c r="H165" s="39"/>
       <c r="I165" s="39"/>
-      <c r="L165" s="29"/>
-      <c r="M165" s="29"/>
+      <c r="L165" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M165" s="29" t="s">
+        <v>60</v>
+      </c>
       <c r="N165" s="5"/>
       <c r="O165" s="5"/>
       <c r="P165" s="5"/>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B166" s="21"/>
-      <c r="C166" s="29"/>
+      <c r="B166" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C166" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="D166" s="21"/>
       <c r="E166" s="24"/>
-      <c r="F166" s="39"/>
+      <c r="F166" s="39" t="s">
+        <v>71</v>
+      </c>
       <c r="G166" s="39"/>
       <c r="H166" s="39"/>
       <c r="I166" s="39"/>
-      <c r="L166" s="29"/>
+      <c r="L166" s="29" t="s">
+        <v>56</v>
+      </c>
       <c r="M166" s="29"/>
       <c r="N166" s="5"/>
       <c r="O166" s="5"/>
@@ -3848,28 +4005,44 @@
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B167" s="21"/>
       <c r="C167" s="29"/>
-      <c r="D167" s="21"/>
-      <c r="E167" s="24"/>
+      <c r="D167" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E167" s="24" t="s">
+        <v>65</v>
+      </c>
       <c r="F167" s="39"/>
       <c r="G167" s="39"/>
       <c r="H167" s="39"/>
       <c r="I167" s="39"/>
-      <c r="L167" s="29"/>
-      <c r="M167" s="29"/>
+      <c r="L167" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M167" s="29" t="s">
+        <v>60</v>
+      </c>
       <c r="N167" s="5"/>
       <c r="O167" s="5"/>
       <c r="P167" s="5"/>
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B168" s="21"/>
-      <c r="C168" s="29"/>
+      <c r="B168" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C168" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="D168" s="21"/>
       <c r="E168" s="24"/>
-      <c r="F168" s="39"/>
+      <c r="F168" s="39" t="s">
+        <v>73</v>
+      </c>
       <c r="G168" s="39"/>
       <c r="H168" s="39"/>
       <c r="I168" s="39"/>
-      <c r="L168" s="29"/>
+      <c r="L168" s="29" t="s">
+        <v>56</v>
+      </c>
       <c r="M168" s="29"/>
       <c r="N168" s="5"/>
       <c r="O168" s="5"/>
@@ -3878,28 +4051,44 @@
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B169" s="21"/>
       <c r="C169" s="29"/>
-      <c r="D169" s="21"/>
-      <c r="E169" s="24"/>
+      <c r="D169" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E169" s="24" t="s">
+        <v>65</v>
+      </c>
       <c r="F169" s="39"/>
       <c r="G169" s="39"/>
       <c r="H169" s="39"/>
       <c r="I169" s="39"/>
-      <c r="L169" s="29"/>
-      <c r="M169" s="29"/>
+      <c r="L169" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M169" s="29" t="s">
+        <v>60</v>
+      </c>
       <c r="N169" s="5"/>
       <c r="O169" s="5"/>
       <c r="P169" s="5"/>
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B170" s="21"/>
-      <c r="C170" s="29"/>
+      <c r="B170" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C170" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="D170" s="21"/>
       <c r="E170" s="24"/>
-      <c r="F170" s="39"/>
+      <c r="F170" s="39" t="s">
+        <v>75</v>
+      </c>
       <c r="G170" s="39"/>
       <c r="H170" s="39"/>
       <c r="I170" s="39"/>
-      <c r="L170" s="29"/>
+      <c r="L170" s="29" t="s">
+        <v>56</v>
+      </c>
       <c r="M170" s="29"/>
       <c r="N170" s="5"/>
       <c r="O170" s="5"/>
@@ -3908,28 +4097,44 @@
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B171" s="21"/>
       <c r="C171" s="29"/>
-      <c r="D171" s="21"/>
-      <c r="E171" s="24"/>
+      <c r="D171" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E171" s="24" t="s">
+        <v>65</v>
+      </c>
       <c r="F171" s="39"/>
       <c r="G171" s="39"/>
       <c r="H171" s="39"/>
       <c r="I171" s="39"/>
-      <c r="L171" s="29"/>
-      <c r="M171" s="29"/>
+      <c r="L171" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M171" s="29" t="s">
+        <v>60</v>
+      </c>
       <c r="N171" s="5"/>
       <c r="O171" s="5"/>
       <c r="P171" s="5"/>
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B172" s="21"/>
-      <c r="C172" s="29"/>
+      <c r="B172" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C172" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="D172" s="21"/>
       <c r="E172" s="24"/>
-      <c r="F172" s="39"/>
+      <c r="F172" s="39" t="s">
+        <v>77</v>
+      </c>
       <c r="G172" s="39"/>
       <c r="H172" s="39"/>
       <c r="I172" s="39"/>
-      <c r="L172" s="29"/>
+      <c r="L172" s="29" t="s">
+        <v>56</v>
+      </c>
       <c r="M172" s="29"/>
       <c r="N172" s="5"/>
       <c r="O172" s="5"/>
@@ -3938,28 +4143,44 @@
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B173" s="21"/>
       <c r="C173" s="29"/>
-      <c r="D173" s="21"/>
-      <c r="E173" s="24"/>
+      <c r="D173" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E173" s="24" t="s">
+        <v>65</v>
+      </c>
       <c r="F173" s="39"/>
       <c r="G173" s="39"/>
       <c r="H173" s="39"/>
       <c r="I173" s="39"/>
-      <c r="L173" s="29"/>
-      <c r="M173" s="29"/>
+      <c r="L173" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M173" s="29" t="s">
+        <v>60</v>
+      </c>
       <c r="N173" s="5"/>
       <c r="O173" s="5"/>
       <c r="P173" s="5"/>
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B174" s="21"/>
-      <c r="C174" s="29"/>
+      <c r="B174" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C174" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="D174" s="21"/>
       <c r="E174" s="24"/>
-      <c r="F174" s="39"/>
+      <c r="F174" s="39" t="s">
+        <v>79</v>
+      </c>
       <c r="G174" s="39"/>
       <c r="H174" s="39"/>
       <c r="I174" s="39"/>
-      <c r="L174" s="29"/>
+      <c r="L174" s="29" t="s">
+        <v>56</v>
+      </c>
       <c r="M174" s="29"/>
       <c r="N174" s="5"/>
       <c r="O174" s="5"/>
@@ -3968,28 +4189,44 @@
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B175" s="21"/>
       <c r="C175" s="29"/>
-      <c r="D175" s="21"/>
-      <c r="E175" s="24"/>
+      <c r="D175" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E175" s="24" t="s">
+        <v>65</v>
+      </c>
       <c r="F175" s="39"/>
       <c r="G175" s="39"/>
       <c r="H175" s="39"/>
       <c r="I175" s="39"/>
-      <c r="L175" s="29"/>
-      <c r="M175" s="29"/>
+      <c r="L175" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M175" s="29" t="s">
+        <v>60</v>
+      </c>
       <c r="N175" s="5"/>
       <c r="O175" s="5"/>
       <c r="P175" s="5"/>
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B176" s="21"/>
-      <c r="C176" s="29"/>
+      <c r="B176" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C176" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="D176" s="21"/>
       <c r="E176" s="24"/>
-      <c r="F176" s="39"/>
+      <c r="F176" s="39" t="s">
+        <v>81</v>
+      </c>
       <c r="G176" s="39"/>
       <c r="H176" s="39"/>
       <c r="I176" s="39"/>
-      <c r="L176" s="29"/>
+      <c r="L176" s="29" t="s">
+        <v>56</v>
+      </c>
       <c r="M176" s="29"/>
       <c r="N176" s="5"/>
       <c r="O176" s="5"/>
@@ -3998,28 +4235,44 @@
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B177" s="21"/>
       <c r="C177" s="29"/>
-      <c r="D177" s="21"/>
-      <c r="E177" s="24"/>
+      <c r="D177" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E177" s="24" t="s">
+        <v>65</v>
+      </c>
       <c r="F177" s="39"/>
       <c r="G177" s="39"/>
       <c r="H177" s="39"/>
       <c r="I177" s="39"/>
-      <c r="L177" s="29"/>
-      <c r="M177" s="29"/>
+      <c r="L177" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M177" s="29" t="s">
+        <v>60</v>
+      </c>
       <c r="N177" s="5"/>
       <c r="O177" s="5"/>
       <c r="P177" s="5"/>
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B178" s="21"/>
-      <c r="C178" s="29"/>
+      <c r="B178" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C178" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="D178" s="21"/>
       <c r="E178" s="24"/>
-      <c r="F178" s="39"/>
+      <c r="F178" s="39" t="s">
+        <v>83</v>
+      </c>
       <c r="G178" s="39"/>
       <c r="H178" s="39"/>
       <c r="I178" s="39"/>
-      <c r="L178" s="29"/>
+      <c r="L178" s="29" t="s">
+        <v>56</v>
+      </c>
       <c r="M178" s="29"/>
       <c r="N178" s="5"/>
       <c r="O178" s="5"/>
@@ -4028,28 +4281,44 @@
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B179" s="21"/>
       <c r="C179" s="29"/>
-      <c r="D179" s="21"/>
-      <c r="E179" s="24"/>
+      <c r="D179" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E179" s="24" t="s">
+        <v>65</v>
+      </c>
       <c r="F179" s="39"/>
       <c r="G179" s="39"/>
       <c r="H179" s="39"/>
       <c r="I179" s="39"/>
-      <c r="L179" s="29"/>
-      <c r="M179" s="29"/>
+      <c r="L179" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M179" s="29" t="s">
+        <v>60</v>
+      </c>
       <c r="N179" s="5"/>
       <c r="O179" s="5"/>
       <c r="P179" s="5"/>
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B180" s="40"/>
-      <c r="C180" s="29"/>
+      <c r="B180" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="C180" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="D180" s="21"/>
       <c r="E180" s="24"/>
-      <c r="F180" s="39"/>
+      <c r="F180" s="39" t="s">
+        <v>85</v>
+      </c>
       <c r="G180" s="39"/>
       <c r="H180" s="39"/>
       <c r="I180" s="39"/>
-      <c r="L180" s="29"/>
+      <c r="L180" s="29" t="s">
+        <v>56</v>
+      </c>
       <c r="M180" s="29"/>
       <c r="N180" s="5"/>
       <c r="O180" s="5"/>
@@ -4058,28 +4327,44 @@
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B181" s="21"/>
       <c r="C181" s="29"/>
-      <c r="D181" s="21"/>
-      <c r="E181" s="24"/>
+      <c r="D181" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E181" s="24" t="s">
+        <v>65</v>
+      </c>
       <c r="F181" s="39"/>
       <c r="G181" s="39"/>
       <c r="H181" s="39"/>
       <c r="I181" s="39"/>
-      <c r="L181" s="29"/>
-      <c r="M181" s="29"/>
+      <c r="L181" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M181" s="29" t="s">
+        <v>60</v>
+      </c>
       <c r="N181" s="5"/>
       <c r="O181" s="5"/>
       <c r="P181" s="5"/>
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B182" s="21"/>
-      <c r="C182" s="29"/>
+      <c r="B182" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C182" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="D182" s="21"/>
       <c r="E182" s="24"/>
-      <c r="F182" s="39"/>
+      <c r="F182" s="39" t="s">
+        <v>87</v>
+      </c>
       <c r="G182" s="39"/>
       <c r="H182" s="39"/>
       <c r="I182" s="39"/>
-      <c r="L182" s="29"/>
+      <c r="L182" s="29" t="s">
+        <v>56</v>
+      </c>
       <c r="M182" s="29"/>
       <c r="N182" s="5"/>
       <c r="O182" s="5"/>
@@ -4088,28 +4373,44 @@
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B183" s="21"/>
       <c r="C183" s="29"/>
-      <c r="D183" s="21"/>
-      <c r="E183" s="24"/>
+      <c r="D183" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E183" s="24" t="s">
+        <v>65</v>
+      </c>
       <c r="F183" s="39"/>
       <c r="G183" s="39"/>
       <c r="H183" s="39"/>
       <c r="I183" s="39"/>
-      <c r="L183" s="29"/>
-      <c r="M183" s="29"/>
+      <c r="L183" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M183" s="29" t="s">
+        <v>60</v>
+      </c>
       <c r="N183" s="5"/>
       <c r="O183" s="5"/>
       <c r="P183" s="5"/>
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B184" s="21"/>
-      <c r="C184" s="29"/>
+      <c r="B184" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C184" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="D184" s="21"/>
       <c r="E184" s="24"/>
-      <c r="F184" s="39"/>
+      <c r="F184" s="39" t="s">
+        <v>89</v>
+      </c>
       <c r="G184" s="39"/>
       <c r="H184" s="39"/>
       <c r="I184" s="39"/>
-      <c r="L184" s="29"/>
+      <c r="L184" s="29" t="s">
+        <v>56</v>
+      </c>
       <c r="M184" s="29"/>
       <c r="N184" s="5"/>
       <c r="O184" s="5"/>
@@ -4118,28 +4419,44 @@
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B185" s="21"/>
       <c r="C185" s="29"/>
-      <c r="D185" s="21"/>
-      <c r="E185" s="24"/>
+      <c r="D185" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E185" s="24" t="s">
+        <v>65</v>
+      </c>
       <c r="F185" s="39"/>
       <c r="G185" s="39"/>
       <c r="H185" s="39"/>
       <c r="I185" s="39"/>
-      <c r="L185" s="29"/>
-      <c r="M185" s="29"/>
+      <c r="L185" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M185" s="29" t="s">
+        <v>60</v>
+      </c>
       <c r="N185" s="5"/>
       <c r="O185" s="5"/>
       <c r="P185" s="5"/>
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B186" s="21"/>
-      <c r="C186" s="29"/>
+      <c r="B186" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C186" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="D186" s="21"/>
       <c r="E186" s="24"/>
-      <c r="F186" s="39"/>
+      <c r="F186" s="39" t="s">
+        <v>91</v>
+      </c>
       <c r="G186" s="39"/>
       <c r="H186" s="39"/>
       <c r="I186" s="39"/>
-      <c r="L186" s="29"/>
+      <c r="L186" s="29" t="s">
+        <v>56</v>
+      </c>
       <c r="M186" s="29"/>
       <c r="N186" s="5"/>
       <c r="O186" s="5"/>
@@ -4148,28 +4465,44 @@
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B187" s="21"/>
       <c r="C187" s="29"/>
-      <c r="D187" s="21"/>
-      <c r="E187" s="24"/>
+      <c r="D187" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E187" s="24" t="s">
+        <v>65</v>
+      </c>
       <c r="F187" s="39"/>
       <c r="G187" s="39"/>
       <c r="H187" s="39"/>
       <c r="I187" s="39"/>
-      <c r="L187" s="29"/>
-      <c r="M187" s="29"/>
+      <c r="L187" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M187" s="29" t="s">
+        <v>60</v>
+      </c>
       <c r="N187" s="5"/>
       <c r="O187" s="5"/>
       <c r="P187" s="5"/>
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B188" s="21"/>
-      <c r="C188" s="29"/>
+      <c r="B188" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C188" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="D188" s="21"/>
       <c r="E188" s="24"/>
-      <c r="F188" s="39"/>
+      <c r="F188" s="39" t="s">
+        <v>93</v>
+      </c>
       <c r="G188" s="39"/>
       <c r="H188" s="39"/>
       <c r="I188" s="39"/>
-      <c r="L188" s="29"/>
+      <c r="L188" s="29" t="s">
+        <v>56</v>
+      </c>
       <c r="M188" s="29"/>
       <c r="N188" s="5"/>
       <c r="O188" s="5"/>
@@ -4178,28 +4511,44 @@
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B189" s="21"/>
       <c r="C189" s="29"/>
-      <c r="D189" s="21"/>
-      <c r="E189" s="24"/>
+      <c r="D189" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E189" s="24" t="s">
+        <v>65</v>
+      </c>
       <c r="F189" s="39"/>
       <c r="G189" s="39"/>
       <c r="H189" s="39"/>
       <c r="I189" s="39"/>
-      <c r="L189" s="29"/>
-      <c r="M189" s="29"/>
+      <c r="L189" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M189" s="29" t="s">
+        <v>60</v>
+      </c>
       <c r="N189" s="5"/>
       <c r="O189" s="5"/>
       <c r="P189" s="5"/>
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B190" s="21"/>
-      <c r="C190" s="29"/>
+      <c r="B190" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C190" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="D190" s="21"/>
       <c r="E190" s="24"/>
-      <c r="F190" s="39"/>
+      <c r="F190" s="39" t="s">
+        <v>95</v>
+      </c>
       <c r="G190" s="39"/>
       <c r="H190" s="39"/>
       <c r="I190" s="39"/>
-      <c r="L190" s="29"/>
+      <c r="L190" s="29" t="s">
+        <v>56</v>
+      </c>
       <c r="M190" s="29"/>
       <c r="N190" s="5"/>
       <c r="O190" s="5"/>
@@ -4208,14 +4557,22 @@
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B191" s="21"/>
       <c r="C191" s="29"/>
-      <c r="D191" s="21"/>
-      <c r="E191" s="24"/>
+      <c r="D191" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E191" s="24" t="s">
+        <v>65</v>
+      </c>
       <c r="F191" s="39"/>
       <c r="G191" s="39"/>
       <c r="H191" s="39"/>
       <c r="I191" s="39"/>
-      <c r="L191" s="29"/>
-      <c r="M191" s="29"/>
+      <c r="L191" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M191" s="29" t="s">
+        <v>60</v>
+      </c>
       <c r="N191" s="5"/>
       <c r="O191" s="5"/>
       <c r="P191" s="5"/>
@@ -4238,10 +4595,10 @@
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="15"/>
       <c r="B193" s="16" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="C193" s="17" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="D193" s="16"/>
       <c r="E193" s="17"/>
@@ -4260,14 +4617,14 @@
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="23"/>
       <c r="B194" s="35" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="C194" s="35" t="s">
         <v>51</v>
       </c>
       <c r="D194" s="38"/>
       <c r="F194" s="1" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="M194" s="35"/>
       <c r="N194" s="35"/>
@@ -4284,7 +4641,7 @@
         <v>54</v>
       </c>
       <c r="F195" s="36" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="G195" s="36" t="s">
         <v>4</v>
@@ -4294,7 +4651,7 @@
       <c r="J195" s="37"/>
       <c r="K195" s="37"/>
       <c r="L195" s="35" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="M195" s="35"/>
       <c r="N195" s="35"/>
@@ -6406,21 +6763,21 @@
       <c r="AMJ202" s="5"/>
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B203" s="5"/>
-      <c r="C203" s="5"/>
-      <c r="D203" s="5"/>
-      <c r="E203" s="5"/>
-      <c r="F203" s="5"/>
-      <c r="G203" s="5"/>
-      <c r="H203" s="5"/>
-      <c r="I203" s="5"/>
-      <c r="J203" s="5"/>
-      <c r="K203" s="5"/>
-      <c r="L203" s="5"/>
-      <c r="M203" s="5"/>
-      <c r="N203" s="5"/>
-      <c r="O203" s="5"/>
-      <c r="P203" s="5"/>
+      <c r="B203" s="35"/>
+      <c r="C203" s="35"/>
+      <c r="D203" s="38"/>
+      <c r="E203" s="36"/>
+      <c r="F203" s="36"/>
+      <c r="G203" s="36"/>
+      <c r="H203" s="36"/>
+      <c r="I203" s="36"/>
+      <c r="J203" s="37"/>
+      <c r="K203" s="37"/>
+      <c r="L203" s="35"/>
+      <c r="M203" s="35"/>
+      <c r="N203" s="35"/>
+      <c r="O203" s="38"/>
+      <c r="P203" s="36"/>
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="26"/>
@@ -6494,10 +6851,10 @@
     </row>
     <row r="208" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B208" s="16" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="C208" s="17" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="D208" s="16"/>
       <c r="E208" s="17"/>
@@ -6535,10 +6892,10 @@
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B211" s="41" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="C211" s="42" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="D211" s="41"/>
       <c r="E211" s="42"/>
@@ -6691,8 +7048,8 @@
   <mergeCells count="1">
     <mergeCell ref="F1:P6"/>
   </mergeCells>
-  <dataValidations count="35">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="J1:J37 J118:J123 J129:J144 J148:J155 J158:K159 J162:K192 J193 J208:J211 K214:K215 J216:J220 J227:J1202" type="none">
+  <dataValidations count="38">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="J1:J37 J118:J123 J129:J144 J148:J155 J158:K192 J193 J208:J211 K214:K215 J216:J220 J227:J1202" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6820,15 +7177,27 @@
       <formula1>"rx,tx"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="The Object code value shall be:&#10;VARIABLE&#10;RECORD&#10;ARRAY" errorStyle="stop" errorTitle="Object Code value" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C156:C157 N156:N157 C194:C202 N194:N202 C221:C226" type="list">
+    <dataValidation allowBlank="true" error="The Object code value shall be:&#10;VARIABLE&#10;RECORD&#10;ARRAY" errorStyle="stop" errorTitle="Object Code value" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="N156:N157 C221:C226" type="list">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="The value for the entry category shall be &#10;M : (mandatory)&#10;O : (optional) &#10;C : (conditional)" errorStyle="stop" errorTitle="Category" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="J156 J195 J197 J199 J201 J222:J226" type="list">
+    <dataValidation allowBlank="true" error="The value for the entry category shall be &#10;M : (mandatory)&#10;O : (optional) &#10;C : (conditional)" errorStyle="stop" errorTitle="Category" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="J222:J226" type="list">
       <formula1>"M,O,C"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="The entry flag shall be&#10;B : (Backup)&#10;S : (Setting)" errorStyle="stop" errorTitle="Backup/Setting Flag" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K156 K195 K197 K199 K201 K222:K226" type="list">
+    <dataValidation allowBlank="true" error="The entry flag shall be&#10;B : (Backup)&#10;S : (Setting)" errorStyle="stop" errorTitle="Backup/Setting Flag" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K222:K226" type="list">
+      <formula1>"B,S"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="The Object code value shall be:&#10;VARIABLE&#10;RECORD&#10;ARRAY" errorStyle="stop" errorTitle="Object Code value" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C156:C157 C194:C203 N194:N203" type="list">
+      <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="The value for the entry category shall be &#10;M : (mandatory)&#10;O : (optional) &#10;C : (conditional)" errorStyle="stop" errorTitle="Category" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="J156 J195 J197 J199 J201 J203" type="list">
+      <formula1>"M,O,C"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="The entry flag shall be&#10;B : (Backup)&#10;S : (Setting)" errorStyle="stop" errorTitle="Backup/Setting Flag" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K156 K195 K197 K199 K201 K203" type="list">
       <formula1>"B,S"</formula1>
       <formula2>0</formula2>
     </dataValidation>
